--- a/output/Results - sem4 (Extended).xlsx
+++ b/output/Results - sem4 (Extended).xlsx
@@ -202,6 +202,12 @@
     <t>RATHNAYAKE M.A.G.K.N.</t>
   </si>
   <si>
+    <t>230121</t>
+  </si>
+  <si>
+    <t>DE MEL D.J.</t>
+  </si>
+  <si>
     <t>230355</t>
   </si>
   <si>
@@ -241,6 +247,12 @@
     <t>COLOMBAGE D.M.</t>
   </si>
   <si>
+    <t>230100</t>
+  </si>
+  <si>
+    <t>CHANDRAKUMARA H.A.D.C.</t>
+  </si>
+  <si>
     <t>230155</t>
   </si>
   <si>
@@ -289,12 +301,6 @@
     <t>GUNASEKARA L.U.A.</t>
   </si>
   <si>
-    <t>230121</t>
-  </si>
-  <si>
-    <t>DE MEL D.J.</t>
-  </si>
-  <si>
     <t>230065</t>
   </si>
   <si>
@@ -376,12 +382,6 @@
     <t>MEEDENIYA M.M.H.</t>
   </si>
   <si>
-    <t>230100</t>
-  </si>
-  <si>
-    <t>CHANDRAKUMARA H.A.D.C.</t>
-  </si>
-  <si>
     <t>230687</t>
   </si>
   <si>
@@ -535,6 +535,12 @@
     <t>ADHIKARI A.H.C.S.</t>
   </si>
   <si>
+    <t>230164</t>
+  </si>
+  <si>
+    <t>DISSANAYAKE R.K.T.</t>
+  </si>
+  <si>
     <t>230052</t>
   </si>
   <si>
@@ -616,12 +622,6 @@
     <t>AMARASINGHE A.A.D.K.</t>
   </si>
   <si>
-    <t>230164</t>
-  </si>
-  <si>
-    <t>DISSANAYAKE R.K.T.</t>
-  </si>
-  <si>
     <t>230477</t>
   </si>
   <si>
@@ -820,10 +820,10 @@
     <t>12(80.0%)</t>
   </si>
   <si>
-    <t>23(23.0%)</t>
-  </si>
-  <si>
-    <t>56(48.7%)</t>
+    <t>24(24.0%)</t>
+  </si>
+  <si>
+    <t>57(49.6%)</t>
   </si>
   <si>
     <t>44(38.3%)</t>
@@ -856,7 +856,7 @@
     <t>3(20.0%)</t>
   </si>
   <si>
-    <t>34(34.0%)</t>
+    <t>33(33.0%)</t>
   </si>
   <si>
     <t>21(18.3%)</t>
@@ -880,7 +880,7 @@
     <t>15(15.0%)</t>
   </si>
   <si>
-    <t>19(16.5%)</t>
+    <t>18(15.7%)</t>
   </si>
   <si>
     <t>4(3.5%)</t>
@@ -1607,7 +1607,7 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
         <v>280</v>
@@ -1699,7 +1699,7 @@
         <v>3</v>
       </c>
       <c r="T5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U5" t="s">
         <v>287</v>
@@ -1883,7 +1883,7 @@
         <v>6</v>
       </c>
       <c r="T7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U7" t="s">
         <v>302</v>
@@ -3099,7 +3099,7 @@
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
@@ -3132,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -3164,10 +3164,10 @@
         <v>20</v>
       </c>
       <c r="J25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
         <v>23</v>
@@ -3185,12 +3185,12 @@
         <v>4</v>
       </c>
       <c r="Q25">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
         <v>68</v>
@@ -3205,10 +3205,10 @@
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
         <v>19</v>
@@ -3220,13 +3220,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L26" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N26" t="s">
         <v>20</v>
@@ -3235,22 +3235,22 @@
         <v>20</v>
       </c>
       <c r="P26">
-        <v>3.964</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
       <c r="D27" t="s">
         <v>23</v>
       </c>
@@ -3273,13 +3273,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M27" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N27" t="s">
         <v>20</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>73</v>
@@ -3305,7 +3305,7 @@
         <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
@@ -3314,7 +3314,7 @@
         <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3326,22 +3326,22 @@
         <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="L28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P28">
-        <v>3.959</v>
+        <v>3.964</v>
       </c>
       <c r="Q28">
         <v>27</v>
@@ -3358,7 +3358,7 @@
         <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -3367,19 +3367,19 @@
         <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="L29" t="s">
         <v>19</v>
@@ -3388,13 +3388,13 @@
         <v>20</v>
       </c>
       <c r="N29" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P29">
-        <v>3.949</v>
+        <v>3.959</v>
       </c>
       <c r="Q29">
         <v>28</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>77</v>
@@ -3411,13 +3411,13 @@
         <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
         <v>19</v>
@@ -3429,13 +3429,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M30" t="s">
         <v>20</v>
@@ -3447,7 +3447,7 @@
         <v>20</v>
       </c>
       <c r="P30">
-        <v>3.945</v>
+        <v>3.959</v>
       </c>
       <c r="Q30">
         <v>29</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>79</v>
@@ -3464,7 +3464,7 @@
         <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
         <v>23</v>
@@ -3479,16 +3479,16 @@
         <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M31" t="s">
         <v>20</v>
@@ -3500,7 +3500,7 @@
         <v>20</v>
       </c>
       <c r="P31">
-        <v>3.945</v>
+        <v>3.949</v>
       </c>
       <c r="Q31">
         <v>30</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>81</v>
@@ -3517,10 +3517,10 @@
         <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         <v>20</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L32" t="s">
         <v>23</v>
@@ -3556,12 +3556,12 @@
         <v>3.945</v>
       </c>
       <c r="Q32">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>83</v>
@@ -3570,7 +3570,7 @@
         <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
         <v>23</v>
@@ -3591,10 +3591,10 @@
         <v>20</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M33" t="s">
         <v>20</v>
@@ -3609,12 +3609,12 @@
         <v>3.945</v>
       </c>
       <c r="Q33">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>85</v>
@@ -3623,7 +3623,7 @@
         <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
         <v>23</v>
@@ -3641,10 +3641,10 @@
         <v>20</v>
       </c>
       <c r="J34" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
@@ -3662,12 +3662,12 @@
         <v>3.945</v>
       </c>
       <c r="Q34">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
         <v>87</v>
@@ -3676,7 +3676,7 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
         <v>23</v>
@@ -3700,7 +3700,7 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M35" t="s">
         <v>20</v>
@@ -3715,12 +3715,12 @@
         <v>3.945</v>
       </c>
       <c r="Q35">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
         <v>89</v>
@@ -3729,7 +3729,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
         <v>23</v>
@@ -3738,7 +3738,7 @@
         <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -3753,7 +3753,7 @@
         <v>20</v>
       </c>
       <c r="L36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
         <v>20</v>
@@ -3768,12 +3768,12 @@
         <v>3.945</v>
       </c>
       <c r="Q36">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>91</v>
@@ -3782,16 +3782,16 @@
         <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
@@ -3800,10 +3800,10 @@
         <v>20</v>
       </c>
       <c r="J37" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -3821,12 +3821,12 @@
         <v>3.945</v>
       </c>
       <c r="Q37">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
         <v>93</v>
@@ -3835,16 +3835,16 @@
         <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E38" t="s">
         <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
         <v>19</v>
@@ -3853,13 +3853,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K38" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M38" t="s">
         <v>20</v>
@@ -3874,12 +3874,12 @@
         <v>3.945</v>
       </c>
       <c r="Q38">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>95</v>
@@ -3888,7 +3888,7 @@
         <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
         <v>23</v>
@@ -3927,12 +3927,12 @@
         <v>3.945</v>
       </c>
       <c r="Q39">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -3941,7 +3941,7 @@
         <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E40" t="s">
         <v>23</v>
@@ -3980,12 +3980,12 @@
         <v>3.945</v>
       </c>
       <c r="Q40">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
@@ -3994,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -4033,12 +4033,12 @@
         <v>3.945</v>
       </c>
       <c r="Q41">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
         <v>101</v>
@@ -4047,7 +4047,7 @@
         <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
@@ -4056,7 +4056,7 @@
         <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -4068,7 +4068,7 @@
         <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L42" t="s">
         <v>23</v>
@@ -4086,12 +4086,12 @@
         <v>3.945</v>
       </c>
       <c r="Q42">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
         <v>103</v>
@@ -4100,7 +4100,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
@@ -4121,10 +4121,10 @@
         <v>20</v>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L43" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
         <v>20</v>
@@ -4139,12 +4139,12 @@
         <v>3.945</v>
       </c>
       <c r="Q43">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
         <v>105</v>
@@ -4153,16 +4153,16 @@
         <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
@@ -4177,27 +4177,27 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M44" t="s">
         <v>20</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P44">
         <v>3.945</v>
       </c>
       <c r="Q44">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
         <v>107</v>
@@ -4206,22 +4206,22 @@
         <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s">
         <v>20</v>
@@ -4230,27 +4230,27 @@
         <v>23</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
         <v>20</v>
       </c>
       <c r="N45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P45">
-        <v>3.925</v>
+        <v>3.945</v>
       </c>
       <c r="Q45">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
@@ -4259,7 +4259,7 @@
         <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
@@ -4271,19 +4271,19 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M46" t="s">
         <v>20</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="47" spans="1:17">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -4312,28 +4312,28 @@
         <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J47" t="s">
         <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L47" t="s">
         <v>23</v>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="48" spans="1:17">
       <c r="A48">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
         <v>113</v>
@@ -4365,22 +4365,22 @@
         <v>114</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="J48" t="s">
         <v>20</v>
@@ -4395,13 +4395,13 @@
         <v>20</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P48">
-        <v>3.918</v>
+        <v>3.925</v>
       </c>
       <c r="Q48">
         <v>47</v>
@@ -4421,7 +4421,7 @@
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -4430,19 +4430,19 @@
         <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
       <c r="J49" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L49" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
         <v>20</v>
@@ -4454,7 +4454,7 @@
         <v>19</v>
       </c>
       <c r="P49">
-        <v>3.904</v>
+        <v>3.918</v>
       </c>
       <c r="Q49">
         <v>48</v>
@@ -4462,49 +4462,49 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" t="s">
         <v>118</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" t="s">
         <v>119</v>
       </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" t="s">
-        <v>23</v>
-      </c>
-      <c r="F50" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" t="s">
-        <v>70</v>
-      </c>
       <c r="M50" t="s">
         <v>20</v>
       </c>
       <c r="N50" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P50">
         <v>3.904</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>120</v>
@@ -4524,7 +4524,7 @@
         <v>121</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E51" t="s">
         <v>23</v>
@@ -4542,13 +4542,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M51" t="s">
         <v>20</v>
@@ -4563,7 +4563,7 @@
         <v>3.904</v>
       </c>
       <c r="Q51">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -4577,7 +4577,7 @@
         <v>123</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
         <v>23</v>
@@ -4592,7 +4592,7 @@
         <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -4630,10 +4630,10 @@
         <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F53" t="s">
         <v>19</v>
@@ -4683,10 +4683,10 @@
         <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -4736,7 +4736,7 @@
         <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
         <v>23</v>
@@ -4789,7 +4789,7 @@
         <v>131</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E56" t="s">
         <v>23</v>
@@ -4842,7 +4842,7 @@
         <v>133</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
@@ -4860,13 +4860,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K57" t="s">
         <v>20</v>
       </c>
       <c r="L57" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M57" t="s">
         <v>20</v>
@@ -4913,13 +4913,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K58" t="s">
         <v>20</v>
       </c>
       <c r="L58" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M58" t="s">
         <v>20</v>
@@ -4948,7 +4948,7 @@
         <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E59" t="s">
         <v>23</v>
@@ -4969,7 +4969,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L59" t="s">
         <v>19</v>
@@ -5001,13 +5001,13 @@
         <v>139</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E60" t="s">
         <v>23</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
         <v>19</v>
@@ -5057,7 +5057,7 @@
         <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>
@@ -5078,7 +5078,7 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M61" t="s">
         <v>20</v>
@@ -5107,10 +5107,10 @@
         <v>143</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F62" t="s">
         <v>23</v>
@@ -5131,7 +5131,7 @@
         <v>19</v>
       </c>
       <c r="L62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M62" t="s">
         <v>20</v>
@@ -5160,7 +5160,7 @@
         <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E63" t="s">
         <v>23</v>
@@ -5175,7 +5175,7 @@
         <v>19</v>
       </c>
       <c r="I63" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J63" t="s">
         <v>23</v>
@@ -5184,7 +5184,7 @@
         <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M63" t="s">
         <v>20</v>
@@ -5213,7 +5213,7 @@
         <v>147</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E64" t="s">
         <v>23</v>
@@ -5228,7 +5228,7 @@
         <v>19</v>
       </c>
       <c r="I64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J64" t="s">
         <v>20</v>
@@ -5237,7 +5237,7 @@
         <v>23</v>
       </c>
       <c r="L64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M64" t="s">
         <v>20</v>
@@ -5322,7 +5322,7 @@
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
         <v>19</v>
@@ -5337,19 +5337,19 @@
         <v>20</v>
       </c>
       <c r="J66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M66" t="s">
         <v>20</v>
       </c>
       <c r="N66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O66" t="s">
         <v>19</v>
@@ -5396,7 +5396,7 @@
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M67" t="s">
         <v>20</v>
@@ -5478,10 +5478,10 @@
         <v>158</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E69" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F69" t="s">
         <v>23</v>
@@ -5587,7 +5587,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F71" t="s">
         <v>23</v>
@@ -5637,10 +5637,10 @@
         <v>164</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F72" t="s">
         <v>19</v>
@@ -5655,13 +5655,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M72" t="s">
         <v>20</v>
@@ -5693,7 +5693,7 @@
         <v>19</v>
       </c>
       <c r="E73" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F73" t="s">
         <v>150</v>
@@ -5705,7 +5705,7 @@
         <v>19</v>
       </c>
       <c r="I73" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J73" t="s">
         <v>23</v>
@@ -5746,7 +5746,7 @@
         <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
@@ -5758,16 +5758,16 @@
         <v>19</v>
       </c>
       <c r="I74" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J74" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K74" t="s">
         <v>20</v>
       </c>
       <c r="L74" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M74" t="s">
         <v>20</v>
@@ -5799,7 +5799,7 @@
         <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F75" t="s">
         <v>23</v>
@@ -5817,13 +5817,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L75" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M75" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N75" t="s">
         <v>20</v>
@@ -5852,7 +5852,7 @@
         <v>23</v>
       </c>
       <c r="E76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s">
         <v>19</v>
@@ -5870,10 +5870,10 @@
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L76" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M76" t="s">
         <v>20</v>
@@ -5902,43 +5902,43 @@
         <v>174</v>
       </c>
       <c r="D77" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H77" t="s">
         <v>19</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="J77" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="K77" t="s">
         <v>20</v>
       </c>
       <c r="L77" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="M77" t="s">
         <v>20</v>
       </c>
       <c r="N77" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P77">
-        <v>3.768</v>
+        <v>3.775</v>
       </c>
       <c r="Q77">
         <v>76</v>
@@ -5955,16 +5955,16 @@
         <v>176</v>
       </c>
       <c r="D78" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="G78" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
         <v>19</v>
@@ -5973,25 +5973,25 @@
         <v>20</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="K78" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="M78" t="s">
         <v>20</v>
       </c>
       <c r="N78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P78">
-        <v>3.763</v>
+        <v>3.768</v>
       </c>
       <c r="Q78">
         <v>77</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="79" spans="1:17">
       <c r="A79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>177</v>
@@ -6008,31 +6008,31 @@
         <v>178</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="E79" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F79" t="s">
         <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H79" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I79" t="s">
         <v>20</v>
       </c>
       <c r="J79" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K79" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L79" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M79" t="s">
         <v>20</v>
@@ -6052,40 +6052,40 @@
     </row>
     <row r="80" spans="1:17">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" t="s">
         <v>180</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>181</v>
       </c>
-      <c r="D80" t="s">
-        <v>117</v>
-      </c>
       <c r="E80" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F80" t="s">
         <v>23</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H80" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K80" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
         <v>20</v>
@@ -6097,7 +6097,7 @@
         <v>20</v>
       </c>
       <c r="P80">
-        <v>3.758</v>
+        <v>3.763</v>
       </c>
       <c r="Q80">
         <v>79</v>
@@ -6114,13 +6114,13 @@
         <v>183</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="E81" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="F81" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G81" t="s">
         <v>23</v>
@@ -6129,16 +6129,16 @@
         <v>19</v>
       </c>
       <c r="I81" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M81" t="s">
         <v>20</v>
@@ -6150,10 +6150,10 @@
         <v>20</v>
       </c>
       <c r="P81">
-        <v>3.75</v>
+        <v>3.758</v>
       </c>
       <c r="Q81">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:17">
@@ -6167,25 +6167,25 @@
         <v>185</v>
       </c>
       <c r="D82" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="E82" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
       </c>
       <c r="G82" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H82" t="s">
         <v>19</v>
       </c>
       <c r="I82" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="J82" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K82" t="s">
         <v>20</v>
@@ -6203,15 +6203,15 @@
         <v>20</v>
       </c>
       <c r="P82">
-        <v>3.745</v>
+        <v>3.75</v>
       </c>
       <c r="Q82">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:17">
       <c r="A83">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>186</v>
@@ -6220,31 +6220,31 @@
         <v>187</v>
       </c>
       <c r="D83" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E83" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="F83" t="s">
         <v>19</v>
       </c>
       <c r="G83" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H83" t="s">
         <v>19</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J83" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="K83" t="s">
         <v>20</v>
       </c>
       <c r="L83" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M83" t="s">
         <v>20</v>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="84" spans="1:17">
       <c r="A84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>188</v>
@@ -6273,31 +6273,31 @@
         <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E84" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H84" t="s">
         <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="K84" t="s">
         <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M84" t="s">
         <v>20</v>
@@ -6309,7 +6309,7 @@
         <v>20</v>
       </c>
       <c r="P84">
-        <v>3.741</v>
+        <v>3.745</v>
       </c>
       <c r="Q84">
         <v>83</v>
@@ -6326,13 +6326,13 @@
         <v>191</v>
       </c>
       <c r="D85" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E85" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G85" t="s">
         <v>19</v>
@@ -6341,16 +6341,16 @@
         <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="J85" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="K85" t="s">
         <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="M85" t="s">
         <v>20</v>
@@ -6362,7 +6362,7 @@
         <v>20</v>
       </c>
       <c r="P85">
-        <v>3.736</v>
+        <v>3.741</v>
       </c>
       <c r="Q85">
         <v>84</v>
@@ -6379,16 +6379,16 @@
         <v>193</v>
       </c>
       <c r="D86" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="E86" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
       </c>
       <c r="G86" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H86" t="s">
         <v>19</v>
@@ -6397,13 +6397,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K86" t="s">
         <v>20</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M86" t="s">
         <v>20</v>
@@ -6415,7 +6415,7 @@
         <v>20</v>
       </c>
       <c r="P86">
-        <v>3.722</v>
+        <v>3.736</v>
       </c>
       <c r="Q86">
         <v>85</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="87" spans="1:17">
       <c r="A87">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" t="s">
         <v>194</v>
@@ -6432,11 +6432,11 @@
         <v>195</v>
       </c>
       <c r="D87" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87" t="s">
         <v>150</v>
       </c>
-      <c r="E87" t="s">
-        <v>70</v>
-      </c>
       <c r="F87" t="s">
         <v>23</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>20</v>
       </c>
       <c r="J87" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K87" t="s">
         <v>20</v>
@@ -6471,12 +6471,12 @@
         <v>3.722</v>
       </c>
       <c r="Q87">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:17">
       <c r="A88">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
         <v>196</v>
@@ -6485,28 +6485,28 @@
         <v>197</v>
       </c>
       <c r="D88" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E88" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
       </c>
       <c r="G88" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H88" t="s">
         <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J88" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="K88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L88" t="s">
         <v>23</v>
@@ -6521,15 +6521,15 @@
         <v>20</v>
       </c>
       <c r="P88">
-        <v>3.716</v>
+        <v>3.722</v>
       </c>
       <c r="Q88">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:17">
       <c r="A89">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" t="s">
         <v>198</v>
@@ -6538,7 +6538,7 @@
         <v>199</v>
       </c>
       <c r="D89" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
         <v>150</v>
@@ -6553,13 +6553,13 @@
         <v>19</v>
       </c>
       <c r="I89" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L89" t="s">
         <v>23</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="90" spans="1:17">
       <c r="A90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>200</v>
@@ -6591,10 +6591,10 @@
         <v>201</v>
       </c>
       <c r="D90" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E90" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -6606,7 +6606,7 @@
         <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J90" t="s">
         <v>23</v>
@@ -6615,7 +6615,7 @@
         <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
         <v>20</v>
@@ -6627,7 +6627,7 @@
         <v>20</v>
       </c>
       <c r="P90">
-        <v>3.708</v>
+        <v>3.716</v>
       </c>
       <c r="Q90">
         <v>89</v>
@@ -6644,10 +6644,10 @@
         <v>203</v>
       </c>
       <c r="D91" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E91" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
         <v>23</v>
@@ -6659,7 +6659,7 @@
         <v>19</v>
       </c>
       <c r="I91" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J91" t="s">
         <v>20</v>
@@ -6668,7 +6668,7 @@
         <v>23</v>
       </c>
       <c r="L91" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M91" t="s">
         <v>20</v>
@@ -6700,7 +6700,7 @@
         <v>20</v>
       </c>
       <c r="E92" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F92" t="s">
         <v>23</v>
@@ -6715,7 +6715,7 @@
         <v>20</v>
       </c>
       <c r="J92" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K92" t="s">
         <v>20</v>
@@ -6750,10 +6750,10 @@
         <v>207</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E93" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
         <v>23</v>
@@ -6806,7 +6806,7 @@
         <v>150</v>
       </c>
       <c r="E94" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -6821,7 +6821,7 @@
         <v>23</v>
       </c>
       <c r="J94" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K94" t="s">
         <v>20</v>
@@ -6859,7 +6859,7 @@
         <v>150</v>
       </c>
       <c r="E95" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -6880,7 +6880,7 @@
         <v>23</v>
       </c>
       <c r="L95" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M95" t="s">
         <v>20</v>
@@ -6912,7 +6912,7 @@
         <v>150</v>
       </c>
       <c r="E96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F96" t="s">
         <v>23</v>
@@ -6933,7 +6933,7 @@
         <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M96" t="s">
         <v>20</v>
@@ -6965,7 +6965,7 @@
         <v>150</v>
       </c>
       <c r="E97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F97" t="s">
         <v>23</v>
@@ -6974,7 +6974,7 @@
         <v>23</v>
       </c>
       <c r="H97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I97" t="s">
         <v>20</v>
@@ -6983,10 +6983,10 @@
         <v>20</v>
       </c>
       <c r="K97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M97" t="s">
         <v>20</v>
@@ -7018,7 +7018,7 @@
         <v>150</v>
       </c>
       <c r="E98" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -7033,7 +7033,7 @@
         <v>20</v>
       </c>
       <c r="J98" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K98" t="s">
         <v>20</v>
@@ -7068,10 +7068,10 @@
         <v>219</v>
       </c>
       <c r="D99" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E99" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -7086,7 +7086,7 @@
         <v>20</v>
       </c>
       <c r="J99" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K99" t="s">
         <v>20</v>
@@ -7121,13 +7121,13 @@
         <v>221</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E100" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F100" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G100" t="s">
         <v>23</v>
@@ -7139,13 +7139,13 @@
         <v>20</v>
       </c>
       <c r="J100" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K100" t="s">
         <v>20</v>
       </c>
       <c r="L100" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M100" t="s">
         <v>20</v>
@@ -7174,10 +7174,10 @@
         <v>223</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E101" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F101" t="s">
         <v>19</v>
@@ -7227,10 +7227,10 @@
         <v>225</v>
       </c>
       <c r="D102" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E102" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
@@ -7248,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="K102" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L102" t="s">
         <v>23</v>
@@ -7280,7 +7280,7 @@
         <v>227</v>
       </c>
       <c r="D103" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E103" t="s">
         <v>23</v>
@@ -7298,13 +7298,13 @@
         <v>20</v>
       </c>
       <c r="J103" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K103" t="s">
         <v>20</v>
       </c>
       <c r="L103" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M103" t="s">
         <v>20</v>
@@ -7333,16 +7333,16 @@
         <v>229</v>
       </c>
       <c r="D104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s">
         <v>19</v>
       </c>
       <c r="G104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H104" t="s">
         <v>23</v>
@@ -7354,10 +7354,10 @@
         <v>20</v>
       </c>
       <c r="K104" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M104" t="s">
         <v>20</v>
@@ -7392,7 +7392,7 @@
         <v>150</v>
       </c>
       <c r="F105" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G105" t="s">
         <v>20</v>
@@ -7404,19 +7404,19 @@
         <v>20</v>
       </c>
       <c r="J105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K105" t="s">
         <v>20</v>
       </c>
       <c r="L105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M105" t="s">
         <v>20</v>
       </c>
       <c r="N105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O105" t="s">
         <v>23</v>
@@ -7442,22 +7442,22 @@
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F106" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G106" t="s">
         <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I106" t="s">
         <v>20</v>
       </c>
       <c r="J106" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K106" t="s">
         <v>20</v>
@@ -7469,7 +7469,7 @@
         <v>20</v>
       </c>
       <c r="N106" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O106" t="s">
         <v>19</v>
@@ -7492,13 +7492,13 @@
         <v>235</v>
       </c>
       <c r="D107" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E107" t="s">
         <v>150</v>
       </c>
       <c r="F107" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G107" t="s">
         <v>23</v>
@@ -7548,10 +7548,10 @@
         <v>150</v>
       </c>
       <c r="E108" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F108" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -7563,7 +7563,7 @@
         <v>20</v>
       </c>
       <c r="J108" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K108" t="s">
         <v>20</v>
@@ -7601,10 +7601,10 @@
         <v>240</v>
       </c>
       <c r="E109" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F109" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G109" t="s">
         <v>23</v>
@@ -7616,7 +7616,7 @@
         <v>20</v>
       </c>
       <c r="J109" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K109" t="s">
         <v>20</v>
@@ -7651,7 +7651,7 @@
         <v>242</v>
       </c>
       <c r="D110" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E110" t="s">
         <v>150</v>
@@ -7669,7 +7669,7 @@
         <v>20</v>
       </c>
       <c r="J110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K110" t="s">
         <v>20</v>
@@ -7725,10 +7725,10 @@
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L111" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M111" t="s">
         <v>20</v>
@@ -7772,7 +7772,7 @@
         <v>23</v>
       </c>
       <c r="I112" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J112" t="s">
         <v>23</v>
@@ -7781,7 +7781,7 @@
         <v>20</v>
       </c>
       <c r="L112" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M112" t="s">
         <v>20</v>
@@ -7810,13 +7810,13 @@
         <v>249</v>
       </c>
       <c r="D113" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E113" t="s">
         <v>245</v>
       </c>
       <c r="F113" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G113" t="s">
         <v>23</v>
@@ -7825,16 +7825,16 @@
         <v>23</v>
       </c>
       <c r="I113" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J113" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K113" t="s">
         <v>20</v>
       </c>
       <c r="L113" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M113" t="s">
         <v>20</v>
@@ -7866,13 +7866,13 @@
         <v>245</v>
       </c>
       <c r="E114" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F114" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G114" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
         <v>23</v>
@@ -7919,28 +7919,28 @@
         <v>240</v>
       </c>
       <c r="E115" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F115" t="s">
         <v>150</v>
       </c>
       <c r="G115" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H115" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I115" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J115" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K115" t="s">
         <v>20</v>
       </c>
       <c r="L115" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M115" t="s">
         <v>20</v>
@@ -7978,7 +7978,7 @@
         <v>23</v>
       </c>
       <c r="G116" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H116" t="s">
         <v>245</v>
@@ -7987,7 +7987,7 @@
         <v>20</v>
       </c>
       <c r="J116" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K116" t="s">
         <v>20</v>
